--- a/excels/枚举定义.xlsx
+++ b/excels/枚举定义.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29100" windowHeight="13380"/>
+    <workbookView windowWidth="29100" windowHeight="13400"/>
   </bookViews>
   <sheets>
     <sheet name="全局枚举表|Enum" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,22 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="20">
+  <si>
+    <t>TAG</t>
+  </si>
+  <si>
+    <t>名称</t>
+  </si>
+  <si>
+    <t>类型/值</t>
+  </si>
+  <si>
+    <t>描述</t>
+  </si>
+  <si>
+    <t>c/s</t>
+  </si>
   <si>
     <t>itemType_BEGIN</t>
   </si>
@@ -1223,14 +1238,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelRow="7" outlineLevelCol="2"/>
+  <dimension ref="A1:D9"/>
+  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelCol="3"/>
   <cols>
-    <col min="1" max="1" width="22.6923076923077" customWidth="1"/>
-    <col min="3" max="3" width="12.7692307692308" customWidth="1"/>
+    <col min="2" max="2" width="22.6923076923077" customWidth="1"/>
+    <col min="4" max="4" width="12.7692307692308" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1240,71 +1255,91 @@
       <c r="C1" t="s">
         <v>2</v>
       </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="2:4">
+      <c r="B3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3">
         <v>1</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="2:4">
+      <c r="B4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4">
+        <v>2</v>
+      </c>
+      <c r="D4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
         <v>4</v>
       </c>
+      <c r="B6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" t="s">
+        <v>6</v>
+      </c>
+      <c r="D6" t="s">
+        <v>13</v>
+      </c>
     </row>
-    <row r="3" spans="1:3">
-      <c r="A3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3">
+    <row r="7" spans="2:4">
+      <c r="B7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7">
+        <v>0</v>
+      </c>
+      <c r="D7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="2:4">
+      <c r="B8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8">
+        <v>1</v>
+      </c>
+      <c r="D8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" spans="2:4">
+      <c r="B9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9">
         <v>2</v>
       </c>
-      <c r="C3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5" t="s">
-        <v>1</v>
-      </c>
-      <c r="C5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6">
-        <v>0</v>
-      </c>
-      <c r="C6" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" t="s">
-        <v>11</v>
-      </c>
-      <c r="B7">
-        <v>1</v>
-      </c>
-      <c r="C7" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" t="s">
-        <v>13</v>
-      </c>
-      <c r="B8">
-        <v>2</v>
-      </c>
-      <c r="C8" t="s">
-        <v>14</v>
+      <c r="D9" t="s">
+        <v>19</v>
       </c>
     </row>
   </sheetData>

--- a/excels/枚举定义.xlsx
+++ b/excels/枚举定义.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29100" windowHeight="13400"/>
+    <workbookView windowWidth="29100" windowHeight="13500"/>
   </bookViews>
   <sheets>
     <sheet name="全局枚举表|Enum" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="26">
   <si>
     <t>TAG</t>
   </si>
@@ -87,6 +87,24 @@
   </si>
   <si>
     <t>金币</t>
+  </si>
+  <si>
+    <t>chatRoomType_BEGIN</t>
+  </si>
+  <si>
+    <t>聊天室类型</t>
+  </si>
+  <si>
+    <t>Server</t>
+  </si>
+  <si>
+    <t>服务器聊天室</t>
+  </si>
+  <si>
+    <t>Group</t>
+  </si>
+  <si>
+    <t>群组聊天室</t>
   </si>
 </sst>
 </file>
@@ -1238,11 +1256,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelCol="3"/>
   <cols>
     <col min="2" max="2" width="22.6923076923077" customWidth="1"/>
-    <col min="4" max="4" width="12.7692307692308" customWidth="1"/>
+    <col min="4" max="4" width="15.1538461538462" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
@@ -1340,6 +1358,42 @@
       </c>
       <c r="D9" t="s">
         <v>19</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" t="s">
+        <v>4</v>
+      </c>
+      <c r="B11" t="s">
+        <v>20</v>
+      </c>
+      <c r="C11" t="s">
+        <v>6</v>
+      </c>
+      <c r="D11" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12" spans="2:4">
+      <c r="B12" t="s">
+        <v>22</v>
+      </c>
+      <c r="C12">
+        <v>1</v>
+      </c>
+      <c r="D12" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="13" spans="2:4">
+      <c r="B13" t="s">
+        <v>24</v>
+      </c>
+      <c r="C13">
+        <v>2</v>
+      </c>
+      <c r="D13" t="s">
+        <v>25</v>
       </c>
     </row>
   </sheetData>
